--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -127,7 +127,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -284,11 +284,44 @@
         <color rgb="00D3D3D3"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -348,6 +381,7 @@
     <xf numFmtId="0" fontId="6" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -773,7 +807,7 @@
           <t>08/09/2026</t>
         </is>
       </c>
-      <c r="I1" s="18" t="n"/>
+      <c r="I1" s="23" t="n"/>
     </row>
     <row r="2" ht="45.75" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="inlineStr">
@@ -854,7 +888,7 @@
         <v>4.1</v>
       </c>
       <c r="I3" s="22" t="n">
-        <v>57</v>
+        <v>4685</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" thickBot="1">
@@ -889,7 +923,7 @@
         <v>3.9</v>
       </c>
       <c r="I4" s="22" t="n">
-        <v>29</v>
+        <v>15615</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" thickBot="1">
@@ -921,10 +955,10 @@
       </c>
       <c r="G5" s="8" t="n"/>
       <c r="H5" s="21" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I5" s="22" t="n">
-        <v>29</v>
+        <v>5065</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" thickBot="1">
@@ -956,10 +990,10 @@
       </c>
       <c r="G6" s="8" t="n"/>
       <c r="H6" s="21" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I6" s="22" t="n">
-        <v>54</v>
+        <v>6376</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" thickBot="1">
@@ -994,7 +1028,7 @@
         <v>3.6</v>
       </c>
       <c r="I7" s="22" t="n">
-        <v>15</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" thickBot="1">
@@ -1029,7 +1063,7 @@
         <v>3.7</v>
       </c>
       <c r="I8" s="22" t="n">
-        <v>28</v>
+        <v>7095</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" thickBot="1">
@@ -1064,7 +1098,7 @@
         <v>4.4</v>
       </c>
       <c r="I9" s="22" t="n">
-        <v>86</v>
+        <v>3563</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" thickBot="1">
@@ -1134,7 +1168,7 @@
         <v>4.3</v>
       </c>
       <c r="I11" s="22" t="n">
-        <v>8</v>
+        <v>877</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" thickBot="1">
@@ -1169,7 +1203,7 @@
         <v>3.9</v>
       </c>
       <c r="I12" s="22" t="n">
-        <v>673</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" thickBot="1">
@@ -1204,7 +1238,7 @@
         <v>3.6</v>
       </c>
       <c r="I13" s="22" t="n">
-        <v>9594</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" thickBot="1">
@@ -1239,7 +1273,7 @@
         <v>3.6</v>
       </c>
       <c r="I14" s="22" t="n">
-        <v>80</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" thickBot="1">
@@ -1274,7 +1308,7 @@
         <v>4.2</v>
       </c>
       <c r="I15" s="22" t="n">
-        <v>999999</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
@@ -1309,7 +1343,7 @@
         <v>4.2</v>
       </c>
       <c r="I16" s="22" t="n">
-        <v>1416</v>
+        <v>781</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" thickBot="1">
@@ -1344,7 +1378,7 @@
         <v>3.9</v>
       </c>
       <c r="I17" s="22" t="n">
-        <v>37</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" thickBot="1">
@@ -1376,7 +1410,7 @@
       </c>
       <c r="G18" s="8" t="n"/>
       <c r="H18" s="21" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I18" s="22" t="n">
         <v>414</v>
@@ -1414,7 +1448,7 @@
         <v>4.2</v>
       </c>
       <c r="I19" s="22" t="n">
-        <v>2468</v>
+        <v>841</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" thickBot="1">
@@ -1519,7 +1553,7 @@
         <v>3.7</v>
       </c>
       <c r="I22" s="22" t="n">
-        <v>539</v>
+        <v>570</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" thickBot="1">
@@ -1554,7 +1588,7 @@
         <v>3.7</v>
       </c>
       <c r="I23" s="22" t="n">
-        <v>3</v>
+        <v>563</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" thickBot="1">
@@ -1589,7 +1623,7 @@
         <v>3.8</v>
       </c>
       <c r="I24" s="22" t="n">
-        <v>70</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" thickBot="1">
@@ -1624,7 +1658,7 @@
         <v>4.7</v>
       </c>
       <c r="I25" s="22" t="n">
-        <v>365</v>
+        <v>546</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" thickBot="1">

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -885,7 +885,7 @@
       </c>
       <c r="G3" s="8" t="n"/>
       <c r="H3" s="21" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="I3" s="22" t="n">
         <v>4685</v>
@@ -920,10 +920,10 @@
       </c>
       <c r="G4" s="8" t="n"/>
       <c r="H4" s="21" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="I4" s="22" t="n">
-        <v>15615</v>
+        <v>15616</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" thickBot="1">
@@ -955,10 +955,10 @@
       </c>
       <c r="G5" s="8" t="n"/>
       <c r="H5" s="21" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I5" s="22" t="n">
-        <v>5065</v>
+        <v>5066</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" thickBot="1">
@@ -990,10 +990,10 @@
       </c>
       <c r="G6" s="8" t="n"/>
       <c r="H6" s="21" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I6" s="22" t="n">
-        <v>6376</v>
+        <v>6380</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" thickBot="1">
@@ -1025,10 +1025,10 @@
       </c>
       <c r="G7" s="8" t="n"/>
       <c r="H7" s="21" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="I7" s="22" t="n">
-        <v>2172</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" thickBot="1">
@@ -1060,10 +1060,10 @@
       </c>
       <c r="G8" s="8" t="n"/>
       <c r="H8" s="21" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="I8" s="22" t="n">
-        <v>7095</v>
+        <v>7094</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" thickBot="1">
@@ -1098,7 +1098,7 @@
         <v>4.4</v>
       </c>
       <c r="I9" s="22" t="n">
-        <v>3563</v>
+        <v>3564</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" thickBot="1">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="G10" s="8" t="n"/>
       <c r="H10" s="21" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I10" s="22" t="n">
         <v>2623</v>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="G11" s="8" t="n"/>
       <c r="H11" s="21" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="I11" s="22" t="n">
         <v>877</v>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="G12" s="8" t="n"/>
       <c r="H12" s="21" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="I12" s="22" t="n">
         <v>1095</v>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="G13" s="8" t="n"/>
       <c r="H13" s="21" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="I13" s="22" t="n">
         <v>2046</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="G14" s="8" t="n"/>
       <c r="H14" s="21" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="I14" s="22" t="n">
         <v>2261</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="G15" s="8" t="n"/>
       <c r="H15" s="21" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I15" s="22" t="n">
         <v>2397</v>
@@ -1340,10 +1340,10 @@
       </c>
       <c r="G16" s="8" t="n"/>
       <c r="H16" s="21" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I16" s="22" t="n">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" thickBot="1">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="G17" s="8" t="n"/>
       <c r="H17" s="21" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="I17" s="22" t="n">
         <v>1222</v>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="G18" s="8" t="n"/>
       <c r="H18" s="21" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I18" s="22" t="n">
         <v>414</v>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="G19" s="8" t="n"/>
       <c r="H19" s="21" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="I19" s="22" t="n">
         <v>841</v>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="21" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="I20" s="22" t="n">
         <v>1016</v>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="21" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="I21" s="22" t="n">
         <v>723</v>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="21" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="I22" s="22" t="n">
         <v>570</v>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="G23" s="8" t="n"/>
       <c r="H23" s="21" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="I23" s="22" t="n">
         <v>563</v>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="21" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="I24" s="22" t="n">
         <v>1402</v>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="21" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="I26" s="22" t="n">
         <v>231</v>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="3" max="3"/>
@@ -808,6 +808,12 @@
         </is>
       </c>
       <c r="I1" s="23" t="n"/>
+      <c r="J1" s="17" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="K1" s="18" t="n"/>
     </row>
     <row r="2" ht="45.75" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="inlineStr">
@@ -851,6 +857,16 @@
         </is>
       </c>
       <c r="I2" s="20" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="J2" s="19" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="K2" s="20" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -890,6 +906,12 @@
       <c r="I3" s="22" t="n">
         <v>4685</v>
       </c>
+      <c r="J3" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K3" s="22" t="n">
+        <v>4692</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A4" s="2" t="n">
@@ -925,6 +947,12 @@
       <c r="I4" s="22" t="n">
         <v>15616</v>
       </c>
+      <c r="J4" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K4" s="22" t="n">
+        <v>15619</v>
+      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" thickBot="1">
       <c r="A5" s="2" t="n">
@@ -960,6 +988,12 @@
       <c r="I5" s="22" t="n">
         <v>5066</v>
       </c>
+      <c r="J5" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K5" s="22" t="n">
+        <v>5069</v>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" thickBot="1">
       <c r="A6" s="2" t="n">
@@ -995,6 +1029,12 @@
       <c r="I6" s="22" t="n">
         <v>6380</v>
       </c>
+      <c r="J6" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K6" s="22" t="n">
+        <v>6389</v>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" thickBot="1">
       <c r="A7" s="2" t="n">
@@ -1030,6 +1070,12 @@
       <c r="I7" s="22" t="n">
         <v>2173</v>
       </c>
+      <c r="J7" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K7" s="22" t="n">
+        <v>2180</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" thickBot="1">
       <c r="A8" s="2" t="n">
@@ -1065,6 +1111,12 @@
       <c r="I8" s="22" t="n">
         <v>7094</v>
       </c>
+      <c r="J8" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K8" s="22" t="n">
+        <v>7096</v>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" thickBot="1">
       <c r="A9" s="2" t="n">
@@ -1100,6 +1152,12 @@
       <c r="I9" s="22" t="n">
         <v>3564</v>
       </c>
+      <c r="J9" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K9" s="22" t="n">
+        <v>3581</v>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" thickBot="1">
       <c r="A10" s="2" t="n">
@@ -1135,6 +1193,12 @@
       <c r="I10" s="22" t="n">
         <v>2623</v>
       </c>
+      <c r="J10" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K10" s="22" t="n">
+        <v>2625</v>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" thickBot="1">
       <c r="A11" s="2" t="n">
@@ -1170,6 +1234,12 @@
       <c r="I11" s="22" t="n">
         <v>877</v>
       </c>
+      <c r="J11" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K11" s="22" t="n">
+        <v>884</v>
+      </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" thickBot="1">
       <c r="A12" s="2" t="n">
@@ -1205,6 +1275,12 @@
       <c r="I12" s="22" t="n">
         <v>1095</v>
       </c>
+      <c r="J12" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K12" s="22" t="n">
+        <v>1096</v>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" thickBot="1">
       <c r="A13" s="2" t="n">
@@ -1240,6 +1316,12 @@
       <c r="I13" s="22" t="n">
         <v>2046</v>
       </c>
+      <c r="J13" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K13" s="22" t="n">
+        <v>2046</v>
+      </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" thickBot="1">
       <c r="A14" s="2" t="n">
@@ -1275,6 +1357,12 @@
       <c r="I14" s="22" t="n">
         <v>2261</v>
       </c>
+      <c r="J14" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K14" s="22" t="n">
+        <v>2248</v>
+      </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" thickBot="1">
       <c r="A15" s="2" t="n">
@@ -1310,6 +1398,12 @@
       <c r="I15" s="22" t="n">
         <v>2397</v>
       </c>
+      <c r="J15" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K15" s="22" t="n">
+        <v>2407</v>
+      </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
       <c r="A16" s="2" t="n">
@@ -1345,6 +1439,12 @@
       <c r="I16" s="22" t="n">
         <v>782</v>
       </c>
+      <c r="J16" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K16" s="22" t="n">
+        <v>783</v>
+      </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" thickBot="1">
       <c r="A17" s="2" t="n">
@@ -1380,6 +1480,12 @@
       <c r="I17" s="22" t="n">
         <v>1222</v>
       </c>
+      <c r="J17" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K17" s="22" t="n">
+        <v>1218</v>
+      </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" thickBot="1">
       <c r="A18" s="2" t="n">
@@ -1415,6 +1521,12 @@
       <c r="I18" s="22" t="n">
         <v>414</v>
       </c>
+      <c r="J18" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K18" s="22" t="n">
+        <v>414</v>
+      </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" thickBot="1">
       <c r="A19" s="2" t="n">
@@ -1450,6 +1562,12 @@
       <c r="I19" s="22" t="n">
         <v>841</v>
       </c>
+      <c r="J19" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K19" s="22" t="n">
+        <v>838</v>
+      </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" thickBot="1">
       <c r="A20" s="2" t="n">
@@ -1485,6 +1603,12 @@
       <c r="I20" s="22" t="n">
         <v>1016</v>
       </c>
+      <c r="J20" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K20" s="22" t="n">
+        <v>1016</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="2" t="n">
@@ -1520,6 +1644,12 @@
       <c r="I21" s="22" t="n">
         <v>723</v>
       </c>
+      <c r="J21" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K21" s="22" t="n">
+        <v>723</v>
+      </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" thickBot="1">
       <c r="A22" s="2" t="n">
@@ -1555,6 +1685,12 @@
       <c r="I22" s="22" t="n">
         <v>570</v>
       </c>
+      <c r="J22" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K22" s="22" t="n">
+        <v>571</v>
+      </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A23" s="2" t="n">
@@ -1590,6 +1726,12 @@
       <c r="I23" s="22" t="n">
         <v>563</v>
       </c>
+      <c r="J23" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K23" s="22" t="n">
+        <v>564</v>
+      </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" thickBot="1">
       <c r="A24" s="2" t="n">
@@ -1625,6 +1767,12 @@
       <c r="I24" s="22" t="n">
         <v>1402</v>
       </c>
+      <c r="J24" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K24" s="22" t="n">
+        <v>1400</v>
+      </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" thickBot="1">
       <c r="A25" s="2" t="n">
@@ -1660,6 +1808,12 @@
       <c r="I25" s="22" t="n">
         <v>546</v>
       </c>
+      <c r="J25" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K25" s="22" t="n">
+        <v>547</v>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" thickBot="1">
       <c r="A26" s="2" t="n">
@@ -1695,9 +1849,16 @@
       <c r="I26" s="22" t="n">
         <v>231</v>
       </c>
+      <c r="J26" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K26" s="22" t="n">
+        <v>231</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
+    <mergeCell ref="J1:K1"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="3" max="3"/>
@@ -813,7 +813,13 @@
           <t>09/09/2026</t>
         </is>
       </c>
-      <c r="K1" s="18" t="n"/>
+      <c r="K1" s="23" t="n"/>
+      <c r="L1" s="17" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+      <c r="M1" s="18" t="n"/>
     </row>
     <row r="2" ht="45.75" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="inlineStr">
@@ -867,6 +873,16 @@
         </is>
       </c>
       <c r="K2" s="20" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="L2" s="19" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="M2" s="20" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -912,6 +928,12 @@
       <c r="K3" s="22" t="n">
         <v>4692</v>
       </c>
+      <c r="L3" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M3" s="22" t="n">
+        <v>4699</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A4" s="2" t="n">
@@ -953,6 +975,12 @@
       <c r="K4" s="22" t="n">
         <v>15619</v>
       </c>
+      <c r="L4" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M4" s="22" t="n">
+        <v>15623</v>
+      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" thickBot="1">
       <c r="A5" s="2" t="n">
@@ -994,6 +1022,12 @@
       <c r="K5" s="22" t="n">
         <v>5069</v>
       </c>
+      <c r="L5" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M5" s="22" t="n">
+        <v>5078</v>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" thickBot="1">
       <c r="A6" s="2" t="n">
@@ -1035,6 +1069,12 @@
       <c r="K6" s="22" t="n">
         <v>6389</v>
       </c>
+      <c r="L6" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M6" s="22" t="n">
+        <v>6396</v>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" thickBot="1">
       <c r="A7" s="2" t="n">
@@ -1076,6 +1116,12 @@
       <c r="K7" s="22" t="n">
         <v>2180</v>
       </c>
+      <c r="L7" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M7" s="22" t="n">
+        <v>2177</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" thickBot="1">
       <c r="A8" s="2" t="n">
@@ -1117,6 +1163,12 @@
       <c r="K8" s="22" t="n">
         <v>7096</v>
       </c>
+      <c r="L8" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M8" s="22" t="n">
+        <v>7109</v>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" thickBot="1">
       <c r="A9" s="2" t="n">
@@ -1158,6 +1210,12 @@
       <c r="K9" s="22" t="n">
         <v>3581</v>
       </c>
+      <c r="L9" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M9" s="22" t="n">
+        <v>3610</v>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" thickBot="1">
       <c r="A10" s="2" t="n">
@@ -1199,6 +1257,12 @@
       <c r="K10" s="22" t="n">
         <v>2625</v>
       </c>
+      <c r="L10" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M10" s="22" t="n">
+        <v>2633</v>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" thickBot="1">
       <c r="A11" s="2" t="n">
@@ -1240,6 +1304,12 @@
       <c r="K11" s="22" t="n">
         <v>884</v>
       </c>
+      <c r="L11" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M11" s="22" t="n">
+        <v>896</v>
+      </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" thickBot="1">
       <c r="A12" s="2" t="n">
@@ -1281,6 +1351,12 @@
       <c r="K12" s="22" t="n">
         <v>1096</v>
       </c>
+      <c r="L12" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M12" s="22" t="n">
+        <v>1096</v>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" thickBot="1">
       <c r="A13" s="2" t="n">
@@ -1322,6 +1398,12 @@
       <c r="K13" s="22" t="n">
         <v>2046</v>
       </c>
+      <c r="L13" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M13" s="22" t="n">
+        <v>2046</v>
+      </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" thickBot="1">
       <c r="A14" s="2" t="n">
@@ -1363,6 +1445,12 @@
       <c r="K14" s="22" t="n">
         <v>2248</v>
       </c>
+      <c r="L14" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M14" s="22" t="n">
+        <v>2245</v>
+      </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" thickBot="1">
       <c r="A15" s="2" t="n">
@@ -1404,6 +1492,12 @@
       <c r="K15" s="22" t="n">
         <v>2407</v>
       </c>
+      <c r="L15" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M15" s="22" t="n">
+        <v>2413</v>
+      </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
       <c r="A16" s="2" t="n">
@@ -1445,6 +1539,12 @@
       <c r="K16" s="22" t="n">
         <v>783</v>
       </c>
+      <c r="L16" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M16" s="22" t="n">
+        <v>784</v>
+      </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" thickBot="1">
       <c r="A17" s="2" t="n">
@@ -1486,6 +1586,12 @@
       <c r="K17" s="22" t="n">
         <v>1218</v>
       </c>
+      <c r="L17" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M17" s="22" t="n">
+        <v>1218</v>
+      </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" thickBot="1">
       <c r="A18" s="2" t="n">
@@ -1527,6 +1633,12 @@
       <c r="K18" s="22" t="n">
         <v>414</v>
       </c>
+      <c r="L18" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M18" s="22" t="n">
+        <v>414</v>
+      </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" thickBot="1">
       <c r="A19" s="2" t="n">
@@ -1568,6 +1680,12 @@
       <c r="K19" s="22" t="n">
         <v>838</v>
       </c>
+      <c r="L19" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M19" s="22" t="n">
+        <v>845</v>
+      </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" thickBot="1">
       <c r="A20" s="2" t="n">
@@ -1609,6 +1727,12 @@
       <c r="K20" s="22" t="n">
         <v>1016</v>
       </c>
+      <c r="L20" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M20" s="22" t="n">
+        <v>1017</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="2" t="n">
@@ -1650,6 +1774,12 @@
       <c r="K21" s="22" t="n">
         <v>723</v>
       </c>
+      <c r="L21" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M21" s="22" t="n">
+        <v>723</v>
+      </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" thickBot="1">
       <c r="A22" s="2" t="n">
@@ -1691,6 +1821,12 @@
       <c r="K22" s="22" t="n">
         <v>571</v>
       </c>
+      <c r="L22" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M22" s="22" t="n">
+        <v>575</v>
+      </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A23" s="2" t="n">
@@ -1732,6 +1868,12 @@
       <c r="K23" s="22" t="n">
         <v>564</v>
       </c>
+      <c r="L23" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M23" s="22" t="n">
+        <v>566</v>
+      </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" thickBot="1">
       <c r="A24" s="2" t="n">
@@ -1773,6 +1915,12 @@
       <c r="K24" s="22" t="n">
         <v>1400</v>
       </c>
+      <c r="L24" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M24" s="22" t="n">
+        <v>1401</v>
+      </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" thickBot="1">
       <c r="A25" s="2" t="n">
@@ -1814,6 +1962,12 @@
       <c r="K25" s="22" t="n">
         <v>547</v>
       </c>
+      <c r="L25" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M25" s="22" t="n">
+        <v>550</v>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" thickBot="1">
       <c r="A26" s="2" t="n">
@@ -1855,13 +2009,20 @@
       <c r="K26" s="22" t="n">
         <v>231</v>
       </c>
+      <c r="L26" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M26" s="22" t="n">
+        <v>238</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="L1:M1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -819,7 +819,7 @@
           <t>10/09/2026</t>
         </is>
       </c>
-      <c r="M1" s="18" t="n"/>
+      <c r="M1" s="23" t="n"/>
     </row>
     <row r="2" ht="45.75" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="inlineStr">
@@ -979,7 +979,7 @@
         <v>4.3</v>
       </c>
       <c r="M4" s="22" t="n">
-        <v>15623</v>
+        <v>15629</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" thickBot="1">
@@ -1073,7 +1073,7 @@
         <v>4.3</v>
       </c>
       <c r="M6" s="22" t="n">
-        <v>6396</v>
+        <v>6401</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" thickBot="1">
@@ -1120,7 +1120,7 @@
         <v>4.5</v>
       </c>
       <c r="M7" s="22" t="n">
-        <v>2177</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" thickBot="1">
@@ -1167,7 +1167,7 @@
         <v>4.3</v>
       </c>
       <c r="M8" s="22" t="n">
-        <v>7109</v>
+        <v>7112</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" thickBot="1">
@@ -1214,7 +1214,7 @@
         <v>4.4</v>
       </c>
       <c r="M9" s="22" t="n">
-        <v>3610</v>
+        <v>3612</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" thickBot="1">
@@ -1261,7 +1261,7 @@
         <v>4.4</v>
       </c>
       <c r="M10" s="22" t="n">
-        <v>2633</v>
+        <v>2637</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" thickBot="1">
@@ -1308,7 +1308,7 @@
         <v>4.7</v>
       </c>
       <c r="M11" s="22" t="n">
-        <v>896</v>
+        <v>897</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" thickBot="1">
@@ -1402,7 +1402,7 @@
         <v>4.7</v>
       </c>
       <c r="M13" s="22" t="n">
-        <v>2046</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" thickBot="1">
@@ -1449,7 +1449,7 @@
         <v>4.4</v>
       </c>
       <c r="M14" s="22" t="n">
-        <v>2245</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" thickBot="1">
@@ -1543,7 +1543,7 @@
         <v>4.5</v>
       </c>
       <c r="M16" s="22" t="n">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" thickBot="1">
@@ -1731,7 +1731,7 @@
         <v>4.6</v>
       </c>
       <c r="M20" s="22" t="n">
-        <v>1017</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" thickBot="1">
@@ -1966,7 +1966,7 @@
         <v>4.7</v>
       </c>
       <c r="M25" s="22" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" thickBot="1">
@@ -2013,7 +2013,7 @@
         <v>4.9</v>
       </c>
       <c r="M26" s="22" t="n">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -1308,7 +1308,7 @@
         <v>4.7</v>
       </c>
       <c r="M11" s="22" t="n">
-        <v>897</v>
+        <v>898</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" thickBot="1">

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="3" max="3"/>
@@ -820,6 +820,12 @@
         </is>
       </c>
       <c r="M1" s="23" t="n"/>
+      <c r="N1" s="17" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+      <c r="O1" s="18" t="n"/>
     </row>
     <row r="2" ht="45.75" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="inlineStr">
@@ -883,6 +889,16 @@
         </is>
       </c>
       <c r="M2" s="20" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="N2" s="19" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="O2" s="20" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -934,6 +950,8 @@
       <c r="M3" s="22" t="n">
         <v>4699</v>
       </c>
+      <c r="N3" s="21" t="n"/>
+      <c r="O3" s="22" t="n"/>
     </row>
     <row r="4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A4" s="2" t="n">
@@ -981,6 +999,8 @@
       <c r="M4" s="22" t="n">
         <v>15629</v>
       </c>
+      <c r="N4" s="21" t="n"/>
+      <c r="O4" s="22" t="n"/>
     </row>
     <row r="5" ht="15.75" customHeight="1" thickBot="1">
       <c r="A5" s="2" t="n">
@@ -1028,6 +1048,8 @@
       <c r="M5" s="22" t="n">
         <v>5078</v>
       </c>
+      <c r="N5" s="21" t="n"/>
+      <c r="O5" s="22" t="n"/>
     </row>
     <row r="6" ht="15.75" customHeight="1" thickBot="1">
       <c r="A6" s="2" t="n">
@@ -1075,6 +1097,8 @@
       <c r="M6" s="22" t="n">
         <v>6401</v>
       </c>
+      <c r="N6" s="21" t="n"/>
+      <c r="O6" s="22" t="n"/>
     </row>
     <row r="7" ht="15.75" customHeight="1" thickBot="1">
       <c r="A7" s="2" t="n">
@@ -1122,6 +1146,8 @@
       <c r="M7" s="22" t="n">
         <v>2178</v>
       </c>
+      <c r="N7" s="21" t="n"/>
+      <c r="O7" s="22" t="n"/>
     </row>
     <row r="8" ht="15.75" customHeight="1" thickBot="1">
       <c r="A8" s="2" t="n">
@@ -1169,6 +1195,8 @@
       <c r="M8" s="22" t="n">
         <v>7112</v>
       </c>
+      <c r="N8" s="21" t="n"/>
+      <c r="O8" s="22" t="n"/>
     </row>
     <row r="9" ht="15.75" customHeight="1" thickBot="1">
       <c r="A9" s="2" t="n">
@@ -1216,6 +1244,8 @@
       <c r="M9" s="22" t="n">
         <v>3612</v>
       </c>
+      <c r="N9" s="21" t="n"/>
+      <c r="O9" s="22" t="n"/>
     </row>
     <row r="10" ht="15.75" customHeight="1" thickBot="1">
       <c r="A10" s="2" t="n">
@@ -1263,6 +1293,8 @@
       <c r="M10" s="22" t="n">
         <v>2637</v>
       </c>
+      <c r="N10" s="21" t="n"/>
+      <c r="O10" s="22" t="n"/>
     </row>
     <row r="11" ht="15.75" customHeight="1" thickBot="1">
       <c r="A11" s="2" t="n">
@@ -1310,6 +1342,8 @@
       <c r="M11" s="22" t="n">
         <v>898</v>
       </c>
+      <c r="N11" s="21" t="n"/>
+      <c r="O11" s="22" t="n"/>
     </row>
     <row r="12" ht="15.75" customHeight="1" thickBot="1">
       <c r="A12" s="2" t="n">
@@ -1357,6 +1391,8 @@
       <c r="M12" s="22" t="n">
         <v>1096</v>
       </c>
+      <c r="N12" s="21" t="n"/>
+      <c r="O12" s="22" t="n"/>
     </row>
     <row r="13" ht="15.75" customHeight="1" thickBot="1">
       <c r="A13" s="2" t="n">
@@ -1404,6 +1440,8 @@
       <c r="M13" s="22" t="n">
         <v>2044</v>
       </c>
+      <c r="N13" s="21" t="n"/>
+      <c r="O13" s="22" t="n"/>
     </row>
     <row r="14" ht="15.75" customHeight="1" thickBot="1">
       <c r="A14" s="2" t="n">
@@ -1451,6 +1489,8 @@
       <c r="M14" s="22" t="n">
         <v>2250</v>
       </c>
+      <c r="N14" s="21" t="n"/>
+      <c r="O14" s="22" t="n"/>
     </row>
     <row r="15" ht="15.75" customHeight="1" thickBot="1">
       <c r="A15" s="2" t="n">
@@ -1498,6 +1538,8 @@
       <c r="M15" s="22" t="n">
         <v>2413</v>
       </c>
+      <c r="N15" s="21" t="n"/>
+      <c r="O15" s="22" t="n"/>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
       <c r="A16" s="2" t="n">
@@ -1545,6 +1587,8 @@
       <c r="M16" s="22" t="n">
         <v>785</v>
       </c>
+      <c r="N16" s="21" t="n"/>
+      <c r="O16" s="22" t="n"/>
     </row>
     <row r="17" ht="15.75" customHeight="1" thickBot="1">
       <c r="A17" s="2" t="n">
@@ -1592,6 +1636,8 @@
       <c r="M17" s="22" t="n">
         <v>1218</v>
       </c>
+      <c r="N17" s="21" t="n"/>
+      <c r="O17" s="22" t="n"/>
     </row>
     <row r="18" ht="15.75" customHeight="1" thickBot="1">
       <c r="A18" s="2" t="n">
@@ -1639,6 +1685,8 @@
       <c r="M18" s="22" t="n">
         <v>414</v>
       </c>
+      <c r="N18" s="21" t="n"/>
+      <c r="O18" s="22" t="n"/>
     </row>
     <row r="19" ht="15.75" customHeight="1" thickBot="1">
       <c r="A19" s="2" t="n">
@@ -1686,6 +1734,8 @@
       <c r="M19" s="22" t="n">
         <v>845</v>
       </c>
+      <c r="N19" s="21" t="n"/>
+      <c r="O19" s="22" t="n"/>
     </row>
     <row r="20" ht="15.75" customHeight="1" thickBot="1">
       <c r="A20" s="2" t="n">
@@ -1733,6 +1783,8 @@
       <c r="M20" s="22" t="n">
         <v>1019</v>
       </c>
+      <c r="N20" s="21" t="n"/>
+      <c r="O20" s="22" t="n"/>
     </row>
     <row r="21" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="2" t="n">
@@ -1780,6 +1832,8 @@
       <c r="M21" s="22" t="n">
         <v>723</v>
       </c>
+      <c r="N21" s="21" t="n"/>
+      <c r="O21" s="22" t="n"/>
     </row>
     <row r="22" ht="15.75" customHeight="1" thickBot="1">
       <c r="A22" s="2" t="n">
@@ -1827,6 +1881,8 @@
       <c r="M22" s="22" t="n">
         <v>575</v>
       </c>
+      <c r="N22" s="21" t="n"/>
+      <c r="O22" s="22" t="n"/>
     </row>
     <row r="23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A23" s="2" t="n">
@@ -1874,6 +1930,8 @@
       <c r="M23" s="22" t="n">
         <v>566</v>
       </c>
+      <c r="N23" s="21" t="n"/>
+      <c r="O23" s="22" t="n"/>
     </row>
     <row r="24" ht="15.75" customHeight="1" thickBot="1">
       <c r="A24" s="2" t="n">
@@ -1921,6 +1979,8 @@
       <c r="M24" s="22" t="n">
         <v>1401</v>
       </c>
+      <c r="N24" s="21" t="n"/>
+      <c r="O24" s="22" t="n"/>
     </row>
     <row r="25" ht="15.75" customHeight="1" thickBot="1">
       <c r="A25" s="2" t="n">
@@ -1968,6 +2028,8 @@
       <c r="M25" s="22" t="n">
         <v>551</v>
       </c>
+      <c r="N25" s="21" t="n"/>
+      <c r="O25" s="22" t="n"/>
     </row>
     <row r="26" ht="15.75" customHeight="1" thickBot="1">
       <c r="A26" s="2" t="n">
@@ -2015,9 +2077,12 @@
       <c r="M26" s="22" t="n">
         <v>242</v>
       </c>
+      <c r="N26" s="21" t="n"/>
+      <c r="O26" s="22" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="N1:O1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="J1:K1"/>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -825,7 +825,7 @@
           <t>11/09/2026</t>
         </is>
       </c>
-      <c r="O1" s="18" t="n"/>
+      <c r="O1" s="23" t="n"/>
     </row>
     <row r="2" ht="45.75" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="inlineStr">

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -950,8 +950,12 @@
       <c r="M3" s="22" t="n">
         <v>4699</v>
       </c>
-      <c r="N3" s="21" t="n"/>
-      <c r="O3" s="22" t="n"/>
+      <c r="N3" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O3" s="22" t="n">
+        <v>4701</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A4" s="2" t="n">
@@ -999,8 +1003,12 @@
       <c r="M4" s="22" t="n">
         <v>15629</v>
       </c>
-      <c r="N4" s="21" t="n"/>
-      <c r="O4" s="22" t="n"/>
+      <c r="N4" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O4" s="22" t="n">
+        <v>15635</v>
+      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" thickBot="1">
       <c r="A5" s="2" t="n">
@@ -1048,8 +1056,12 @@
       <c r="M5" s="22" t="n">
         <v>5078</v>
       </c>
-      <c r="N5" s="21" t="n"/>
-      <c r="O5" s="22" t="n"/>
+      <c r="N5" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O5" s="22" t="n">
+        <v>5089</v>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" thickBot="1">
       <c r="A6" s="2" t="n">
@@ -1097,8 +1109,12 @@
       <c r="M6" s="22" t="n">
         <v>6401</v>
       </c>
-      <c r="N6" s="21" t="n"/>
-      <c r="O6" s="22" t="n"/>
+      <c r="N6" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O6" s="22" t="n">
+        <v>6409</v>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" thickBot="1">
       <c r="A7" s="2" t="n">
@@ -1146,8 +1162,12 @@
       <c r="M7" s="22" t="n">
         <v>2178</v>
       </c>
-      <c r="N7" s="21" t="n"/>
-      <c r="O7" s="22" t="n"/>
+      <c r="N7" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O7" s="22" t="n">
+        <v>2179</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" thickBot="1">
       <c r="A8" s="2" t="n">
@@ -1195,8 +1215,12 @@
       <c r="M8" s="22" t="n">
         <v>7112</v>
       </c>
-      <c r="N8" s="21" t="n"/>
-      <c r="O8" s="22" t="n"/>
+      <c r="N8" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O8" s="22" t="n">
+        <v>7118</v>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" thickBot="1">
       <c r="A9" s="2" t="n">
@@ -1244,8 +1268,12 @@
       <c r="M9" s="22" t="n">
         <v>3612</v>
       </c>
-      <c r="N9" s="21" t="n"/>
-      <c r="O9" s="22" t="n"/>
+      <c r="N9" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O9" s="22" t="n">
+        <v>3618</v>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" thickBot="1">
       <c r="A10" s="2" t="n">
@@ -1293,8 +1321,12 @@
       <c r="M10" s="22" t="n">
         <v>2637</v>
       </c>
-      <c r="N10" s="21" t="n"/>
-      <c r="O10" s="22" t="n"/>
+      <c r="N10" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O10" s="22" t="n">
+        <v>2640</v>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" thickBot="1">
       <c r="A11" s="2" t="n">
@@ -1342,8 +1374,12 @@
       <c r="M11" s="22" t="n">
         <v>898</v>
       </c>
-      <c r="N11" s="21" t="n"/>
-      <c r="O11" s="22" t="n"/>
+      <c r="N11" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O11" s="22" t="n">
+        <v>908</v>
+      </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" thickBot="1">
       <c r="A12" s="2" t="n">
@@ -1391,8 +1427,12 @@
       <c r="M12" s="22" t="n">
         <v>1096</v>
       </c>
-      <c r="N12" s="21" t="n"/>
-      <c r="O12" s="22" t="n"/>
+      <c r="N12" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O12" s="22" t="n">
+        <v>1097</v>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" thickBot="1">
       <c r="A13" s="2" t="n">
@@ -1440,8 +1480,12 @@
       <c r="M13" s="22" t="n">
         <v>2044</v>
       </c>
-      <c r="N13" s="21" t="n"/>
-      <c r="O13" s="22" t="n"/>
+      <c r="N13" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O13" s="22" t="n">
+        <v>2059</v>
+      </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" thickBot="1">
       <c r="A14" s="2" t="n">
@@ -1489,8 +1533,12 @@
       <c r="M14" s="22" t="n">
         <v>2250</v>
       </c>
-      <c r="N14" s="21" t="n"/>
-      <c r="O14" s="22" t="n"/>
+      <c r="N14" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O14" s="22" t="n">
+        <v>2260</v>
+      </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" thickBot="1">
       <c r="A15" s="2" t="n">
@@ -1538,8 +1586,12 @@
       <c r="M15" s="22" t="n">
         <v>2413</v>
       </c>
-      <c r="N15" s="21" t="n"/>
-      <c r="O15" s="22" t="n"/>
+      <c r="N15" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O15" s="22" t="n">
+        <v>2427</v>
+      </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
       <c r="A16" s="2" t="n">
@@ -1587,8 +1639,12 @@
       <c r="M16" s="22" t="n">
         <v>785</v>
       </c>
-      <c r="N16" s="21" t="n"/>
-      <c r="O16" s="22" t="n"/>
+      <c r="N16" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O16" s="22" t="n">
+        <v>785</v>
+      </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" thickBot="1">
       <c r="A17" s="2" t="n">
@@ -1636,8 +1692,12 @@
       <c r="M17" s="22" t="n">
         <v>1218</v>
       </c>
-      <c r="N17" s="21" t="n"/>
-      <c r="O17" s="22" t="n"/>
+      <c r="N17" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O17" s="22" t="n">
+        <v>1219</v>
+      </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" thickBot="1">
       <c r="A18" s="2" t="n">
@@ -1685,8 +1745,12 @@
       <c r="M18" s="22" t="n">
         <v>414</v>
       </c>
-      <c r="N18" s="21" t="n"/>
-      <c r="O18" s="22" t="n"/>
+      <c r="N18" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O18" s="22" t="n">
+        <v>414</v>
+      </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" thickBot="1">
       <c r="A19" s="2" t="n">
@@ -1734,8 +1798,12 @@
       <c r="M19" s="22" t="n">
         <v>845</v>
       </c>
-      <c r="N19" s="21" t="n"/>
-      <c r="O19" s="22" t="n"/>
+      <c r="N19" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O19" s="22" t="n">
+        <v>849</v>
+      </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" thickBot="1">
       <c r="A20" s="2" t="n">
@@ -1783,8 +1851,12 @@
       <c r="M20" s="22" t="n">
         <v>1019</v>
       </c>
-      <c r="N20" s="21" t="n"/>
-      <c r="O20" s="22" t="n"/>
+      <c r="N20" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O20" s="22" t="n">
+        <v>1020</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="2" t="n">
@@ -1832,8 +1904,12 @@
       <c r="M21" s="22" t="n">
         <v>723</v>
       </c>
-      <c r="N21" s="21" t="n"/>
-      <c r="O21" s="22" t="n"/>
+      <c r="N21" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O21" s="22" t="n">
+        <v>723</v>
+      </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" thickBot="1">
       <c r="A22" s="2" t="n">
@@ -1881,8 +1957,12 @@
       <c r="M22" s="22" t="n">
         <v>575</v>
       </c>
-      <c r="N22" s="21" t="n"/>
-      <c r="O22" s="22" t="n"/>
+      <c r="N22" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O22" s="22" t="n">
+        <v>581</v>
+      </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A23" s="2" t="n">
@@ -1930,8 +2010,12 @@
       <c r="M23" s="22" t="n">
         <v>566</v>
       </c>
-      <c r="N23" s="21" t="n"/>
-      <c r="O23" s="22" t="n"/>
+      <c r="N23" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O23" s="22" t="n">
+        <v>723</v>
+      </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" thickBot="1">
       <c r="A24" s="2" t="n">
@@ -1979,8 +2063,12 @@
       <c r="M24" s="22" t="n">
         <v>1401</v>
       </c>
-      <c r="N24" s="21" t="n"/>
-      <c r="O24" s="22" t="n"/>
+      <c r="N24" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O24" s="22" t="n">
+        <v>1399</v>
+      </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" thickBot="1">
       <c r="A25" s="2" t="n">
@@ -2028,8 +2116,12 @@
       <c r="M25" s="22" t="n">
         <v>551</v>
       </c>
-      <c r="N25" s="21" t="n"/>
-      <c r="O25" s="22" t="n"/>
+      <c r="N25" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O25" s="22" t="n">
+        <v>552</v>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" thickBot="1">
       <c r="A26" s="2" t="n">
@@ -2077,8 +2169,12 @@
       <c r="M26" s="22" t="n">
         <v>242</v>
       </c>
-      <c r="N26" s="21" t="n"/>
-      <c r="O26" s="22" t="n"/>
+      <c r="N26" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O26" s="22" t="n">
+        <v>242</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -954,7 +954,7 @@
         <v>4.4</v>
       </c>
       <c r="O3" s="22" t="n">
-        <v>4701</v>
+        <v>4703</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" thickBot="1">
@@ -1007,7 +1007,7 @@
         <v>4.3</v>
       </c>
       <c r="O4" s="22" t="n">
-        <v>15635</v>
+        <v>15636</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" thickBot="1">
@@ -1060,7 +1060,7 @@
         <v>4.4</v>
       </c>
       <c r="O5" s="22" t="n">
-        <v>5089</v>
+        <v>5092</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" thickBot="1">
@@ -1113,7 +1113,7 @@
         <v>4.3</v>
       </c>
       <c r="O6" s="22" t="n">
-        <v>6409</v>
+        <v>6411</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" thickBot="1">
@@ -1166,7 +1166,7 @@
         <v>4.5</v>
       </c>
       <c r="O7" s="22" t="n">
-        <v>2179</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" thickBot="1">
@@ -1219,7 +1219,7 @@
         <v>4.4</v>
       </c>
       <c r="O8" s="22" t="n">
-        <v>7118</v>
+        <v>7119</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" thickBot="1">
@@ -1272,7 +1272,7 @@
         <v>4.4</v>
       </c>
       <c r="O9" s="22" t="n">
-        <v>3618</v>
+        <v>3612</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" thickBot="1">
@@ -1325,7 +1325,7 @@
         <v>4.4</v>
       </c>
       <c r="O10" s="22" t="n">
-        <v>2640</v>
+        <v>2645</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" thickBot="1">
@@ -1378,7 +1378,7 @@
         <v>4.7</v>
       </c>
       <c r="O11" s="22" t="n">
-        <v>908</v>
+        <v>909</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" thickBot="1">
@@ -1484,7 +1484,7 @@
         <v>4.7</v>
       </c>
       <c r="O13" s="22" t="n">
-        <v>2059</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" thickBot="1">
@@ -1537,7 +1537,7 @@
         <v>4.4</v>
       </c>
       <c r="O14" s="22" t="n">
-        <v>2260</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" thickBot="1">
@@ -1590,7 +1590,7 @@
         <v>4.4</v>
       </c>
       <c r="O15" s="22" t="n">
-        <v>2427</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
@@ -1696,7 +1696,7 @@
         <v>4.7</v>
       </c>
       <c r="O17" s="22" t="n">
-        <v>1219</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" thickBot="1">
@@ -1802,7 +1802,7 @@
         <v>4.7</v>
       </c>
       <c r="O19" s="22" t="n">
-        <v>849</v>
+        <v>851</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" thickBot="1">
@@ -1855,7 +1855,7 @@
         <v>4.6</v>
       </c>
       <c r="O20" s="22" t="n">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" thickBot="1">
@@ -2067,7 +2067,7 @@
         <v>4.9</v>
       </c>
       <c r="O24" s="22" t="n">
-        <v>1399</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" thickBot="1">
@@ -2120,7 +2120,7 @@
         <v>4.7</v>
       </c>
       <c r="O25" s="22" t="n">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" thickBot="1">

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="3" max="3"/>
@@ -826,6 +826,12 @@
         </is>
       </c>
       <c r="O1" s="23" t="n"/>
+      <c r="P1" s="17" t="inlineStr">
+        <is>
+          <t>12/09/2026</t>
+        </is>
+      </c>
+      <c r="Q1" s="18" t="n"/>
     </row>
     <row r="2" ht="45.75" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="inlineStr">
@@ -899,6 +905,16 @@
         </is>
       </c>
       <c r="O2" s="20" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="P2" s="19" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="Q2" s="20" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -956,6 +972,12 @@
       <c r="O3" s="22" t="n">
         <v>4703</v>
       </c>
+      <c r="P3" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q3" s="22" t="n">
+        <v>4703</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A4" s="2" t="n">
@@ -1009,6 +1031,12 @@
       <c r="O4" s="22" t="n">
         <v>15636</v>
       </c>
+      <c r="P4" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Q4" s="22" t="n">
+        <v>15644</v>
+      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" thickBot="1">
       <c r="A5" s="2" t="n">
@@ -1062,6 +1090,12 @@
       <c r="O5" s="22" t="n">
         <v>5092</v>
       </c>
+      <c r="P5" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q5" s="22" t="n">
+        <v>5093</v>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" thickBot="1">
       <c r="A6" s="2" t="n">
@@ -1115,6 +1149,12 @@
       <c r="O6" s="22" t="n">
         <v>6411</v>
       </c>
+      <c r="P6" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Q6" s="22" t="n">
+        <v>6410</v>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" thickBot="1">
       <c r="A7" s="2" t="n">
@@ -1168,6 +1208,12 @@
       <c r="O7" s="22" t="n">
         <v>2184</v>
       </c>
+      <c r="P7" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q7" s="22" t="n">
+        <v>2190</v>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" thickBot="1">
       <c r="A8" s="2" t="n">
@@ -1221,6 +1267,12 @@
       <c r="O8" s="22" t="n">
         <v>7119</v>
       </c>
+      <c r="P8" s="21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Q8" s="22" t="n">
+        <v>7112</v>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" thickBot="1">
       <c r="A9" s="2" t="n">
@@ -1274,6 +1326,12 @@
       <c r="O9" s="22" t="n">
         <v>3612</v>
       </c>
+      <c r="P9" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q9" s="22" t="n">
+        <v>3593</v>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" thickBot="1">
       <c r="A10" s="2" t="n">
@@ -1327,6 +1385,12 @@
       <c r="O10" s="22" t="n">
         <v>2645</v>
       </c>
+      <c r="P10" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q10" s="22" t="n">
+        <v>2649</v>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" thickBot="1">
       <c r="A11" s="2" t="n">
@@ -1380,6 +1444,12 @@
       <c r="O11" s="22" t="n">
         <v>909</v>
       </c>
+      <c r="P11" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Q11" s="22" t="n">
+        <v>919</v>
+      </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" thickBot="1">
       <c r="A12" s="2" t="n">
@@ -1433,6 +1503,12 @@
       <c r="O12" s="22" t="n">
         <v>1097</v>
       </c>
+      <c r="P12" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q12" s="22" t="n">
+        <v>1098</v>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" thickBot="1">
       <c r="A13" s="2" t="n">
@@ -1486,6 +1562,12 @@
       <c r="O13" s="22" t="n">
         <v>2057</v>
       </c>
+      <c r="P13" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Q13" s="22" t="n">
+        <v>2055</v>
+      </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" thickBot="1">
       <c r="A14" s="2" t="n">
@@ -1539,6 +1621,12 @@
       <c r="O14" s="22" t="n">
         <v>2264</v>
       </c>
+      <c r="P14" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q14" s="22" t="n">
+        <v>2275</v>
+      </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" thickBot="1">
       <c r="A15" s="2" t="n">
@@ -1592,6 +1680,12 @@
       <c r="O15" s="22" t="n">
         <v>2430</v>
       </c>
+      <c r="P15" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q15" s="22" t="n">
+        <v>2440</v>
+      </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
       <c r="A16" s="2" t="n">
@@ -1645,6 +1739,12 @@
       <c r="O16" s="22" t="n">
         <v>785</v>
       </c>
+      <c r="P16" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q16" s="22" t="n">
+        <v>785</v>
+      </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" thickBot="1">
       <c r="A17" s="2" t="n">
@@ -1698,6 +1798,12 @@
       <c r="O17" s="22" t="n">
         <v>1220</v>
       </c>
+      <c r="P17" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Q17" s="22" t="n">
+        <v>1220</v>
+      </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" thickBot="1">
       <c r="A18" s="2" t="n">
@@ -1751,6 +1857,12 @@
       <c r="O18" s="22" t="n">
         <v>414</v>
       </c>
+      <c r="P18" s="21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q18" s="22" t="n">
+        <v>414</v>
+      </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" thickBot="1">
       <c r="A19" s="2" t="n">
@@ -1804,6 +1916,12 @@
       <c r="O19" s="22" t="n">
         <v>851</v>
       </c>
+      <c r="P19" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Q19" s="22" t="n">
+        <v>851</v>
+      </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" thickBot="1">
       <c r="A20" s="2" t="n">
@@ -1857,6 +1975,12 @@
       <c r="O20" s="22" t="n">
         <v>1021</v>
       </c>
+      <c r="P20" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Q20" s="22" t="n">
+        <v>1022</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="2" t="n">
@@ -1910,6 +2034,12 @@
       <c r="O21" s="22" t="n">
         <v>723</v>
       </c>
+      <c r="P21" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Q21" s="22" t="n">
+        <v>722</v>
+      </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" thickBot="1">
       <c r="A22" s="2" t="n">
@@ -1963,6 +2093,12 @@
       <c r="O22" s="22" t="n">
         <v>581</v>
       </c>
+      <c r="P22" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Q22" s="22" t="n">
+        <v>583</v>
+      </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A23" s="2" t="n">
@@ -2016,6 +2152,12 @@
       <c r="O23" s="22" t="n">
         <v>723</v>
       </c>
+      <c r="P23" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Q23" s="22" t="n">
+        <v>722</v>
+      </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" thickBot="1">
       <c r="A24" s="2" t="n">
@@ -2069,6 +2211,12 @@
       <c r="O24" s="22" t="n">
         <v>1400</v>
       </c>
+      <c r="P24" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Q24" s="22" t="n">
+        <v>1403</v>
+      </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" thickBot="1">
       <c r="A25" s="2" t="n">
@@ -2122,6 +2270,12 @@
       <c r="O25" s="22" t="n">
         <v>553</v>
       </c>
+      <c r="P25" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Q25" s="22" t="n">
+        <v>562</v>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" thickBot="1">
       <c r="A26" s="2" t="n">
@@ -2175,13 +2329,20 @@
       <c r="O26" s="22" t="n">
         <v>242</v>
       </c>
+      <c r="P26" s="21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Q26" s="22" t="n">
+        <v>251</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="J1:K1"/>
+    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="F1:G1"/>
   </mergeCells>
